--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_285_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_285_R29.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.255</v>
+        <v>2.7006</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7185</v>
+        <v>2.2649</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5365</v>
+        <v>0.4357</v>
       </c>
       <c r="G2" t="n">
         <v>2.217</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.4984</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5816</v>
+        <v>-0.0351</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3624</v>
+        <v>-0.4632</v>
       </c>
       <c r="V2" t="n">
         <v>1.214</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0177</v>
+        <v>0.9916</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0669</v>
+        <v>0.0078</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0846</v>
+        <v>0.9838</v>
       </c>
       <c r="G3" t="n">
         <v>0.629</v>
@@ -688,13 +688,13 @@
         <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0751</v>
+        <v>-0.1013</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.224</v>
+        <v>-0.1494</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0134</v>
+        <v>0.9462</v>
       </c>
       <c r="E4" t="n">
         <v>1.9682</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9548</v>
+        <v>-1.022</v>
       </c>
       <c r="G4" t="n">
         <v>0.5864</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.427</v>
+        <v>0.3598</v>
       </c>
       <c r="T4" t="n">
         <v>0.5702</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1432</v>
+        <v>-0.2104</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1101</v>
+        <v>-1.272</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6947</v>
+        <v>0.2976</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8048</v>
+        <v>-1.5696</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5381</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1261</v>
+        <v>-0.288</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5034</v>
+        <v>0.1063</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6778999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7594</v>
+        <v>-2.1554</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0709</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8303</v>
+        <v>-2.7295</v>
       </c>
       <c r="G6" t="n">
         <v>-3.6698</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4659</v>
+        <v>-0.8619</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.963</v>
+        <v>-0.4597</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.503</v>
+        <v>-0.4022</v>
       </c>
       <c r="V6" t="n">
         <v>2.1444</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9805</v>
+        <v>-2.5281</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3577</v>
+        <v>-0.9725</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6228</v>
+        <v>-1.5556</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8013</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6431</v>
+        <v>-0.1907</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7468</v>
+        <v>-0.3615</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1037</v>
+        <v>0.1709</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.731</v>
+        <v>-2.7663</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5963</v>
+        <v>2.2921</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.3273</v>
+        <v>-5.0585</v>
       </c>
       <c r="G8" t="n">
         <v>-5.7617</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1833</v>
+        <v>-1.2186</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.2513</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2362</v>
+        <v>-0.9673</v>
       </c>
       <c r="V8" t="n">
         <v>2.8223</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8361</v>
+        <v>-3.351</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5938</v>
+        <v>-0.5332</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2423</v>
+        <v>-2.8178</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3257</v>
+        <v>-3.979</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3878</v>
+        <v>-0.0073</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7135</v>
+        <v>-3.9717</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3796</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0923</v>
+        <v>1.4018</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7127</v>
+        <v>-2.2854</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7053</v>
+        <v>-3.0953</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7045</v>
+        <v>-1.4091</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0008</v>
+        <v>-1.6862</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3506</v>
+        <v>-0.3695</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3462</v>
+        <v>0.2087</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6967</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.999</v>
+        <v>-3.43</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3156</v>
+        <v>-0.7218</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6834</v>
+        <v>-2.7083</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.979</v>
+        <v>-1.0464</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0073</v>
+        <v>-0.2232</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9717</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8836000000000001</v>
+        <v>0.5871</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4018</v>
+        <v>0.3564</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2854</v>
+        <v>0.2308</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0953</v>
+        <v>-1.6335</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4091</v>
+        <v>-0.5796</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6862</v>
+        <v>-1.0539</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0174</v>
+        <v>-0.5434</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5737</v>
+        <v>-0.1491</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4437</v>
+        <v>-0.3943</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3943</v>
+        <v>-1.6083</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4044</v>
+        <v>-4.0555</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4609</v>
+        <v>-1.9476</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9435</v>
+        <v>-2.1079</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0464</v>
+        <v>-2.3257</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2232</v>
+        <v>0.3878</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-2.7135</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5871</v>
+        <v>0.3796</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3564</v>
+        <v>1.0923</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2308</v>
+        <v>-0.7127</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6335</v>
+        <v>-2.7053</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5796</v>
+        <v>-0.7045</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0539</v>
+        <v>-2.0008</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5178</v>
+        <v>-0.57</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8883</v>
+        <v>-0.0077</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.5623</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3028</v>
+        <v>-6.9021</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4269</v>
+        <v>-5.4885</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8759</v>
+        <v>-1.4136</v>
       </c>
       <c r="G12" t="n">
         <v>-5.251</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3399</v>
+        <v>-0.2594</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1879</v>
+        <v>0.1263</v>
       </c>
       <c r="U12" t="n">
-        <v>0.152</v>
+        <v>-0.3857</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.3568</v>
+        <v>-8.251899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.634</v>
+        <v>-4.4282</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7228</v>
+        <v>-3.8236</v>
       </c>
       <c r="G13" t="n">
         <v>-4.3812</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9159</v>
+        <v>0.0209</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3372</v>
+        <v>0.543</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4213</v>
+        <v>-0.5221</v>
       </c>
       <c r="V13" t="n">
         <v>0.2836</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-31.194</v>
+        <v>-30.0739</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.8072</v>
+        <v>-6.687100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-23.3868</v>
+        <v>-23.3869</v>
       </c>
       <c r="G14" t="n">
         <v>-25.3218</v>
@@ -1537,7 +1537,7 @@
         <v>-15.0223</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.4793</v>
+        <v>-3.479299999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.9172</v>
@@ -1546,10 +1546,10 @@
         <v>10.438</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.640600000000001</v>
+        <v>-4.5205</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9796000000000002</v>
+        <v>0.1407000000000002</v>
       </c>
       <c r="U14" t="n">
         <v>-4.6609</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3273</v>
+        <v>5.929</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2364</v>
+        <v>4.4672</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0908</v>
+        <v>1.4618</v>
       </c>
       <c r="G15" t="n">
         <v>5.4721</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0871</v>
+        <v>0.6888</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3239</v>
+        <v>0.5546</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2368</v>
+        <v>0.1342</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1397</v>
+        <v>5.7364</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3323</v>
+        <v>4.8605</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8074</v>
+        <v>0.8759</v>
       </c>
       <c r="G16" t="n">
         <v>4.3502</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1659</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1246</v>
+        <v>0.6528</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0413</v>
+        <v>0.1098</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6728</v>
+        <v>5.4654</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1864</v>
+        <v>2.8325</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4864</v>
+        <v>2.6329</v>
       </c>
       <c r="G17" t="n">
         <v>3.5611</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4132</v>
+        <v>1.2059</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1993</v>
+        <v>0.8454</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2139</v>
+        <v>0.3605</v>
       </c>
       <c r="V17" t="n">
         <v>0.9304</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.8657</v>
+        <v>4.7992</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3168</v>
+        <v>3.5527</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5489</v>
+        <v>1.2464</v>
       </c>
       <c r="G18" t="n">
         <v>2.3415</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1505</v>
+        <v>1.084</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0351</v>
+        <v>0.2008</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1857</v>
+        <v>0.8832</v>
       </c>
       <c r="V18" t="n">
         <v>0.6778999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7683</v>
+        <v>3.5946</v>
       </c>
       <c r="E19" t="n">
-        <v>1.327</v>
+        <v>1.9168</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4413</v>
+        <v>1.6778</v>
       </c>
       <c r="G19" t="n">
         <v>0.7818000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1103</v>
+        <v>0.9366</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>0.291</v>
       </c>
       <c r="U19" t="n">
-        <v>0.409</v>
+        <v>0.6456</v>
       </c>
       <c r="V19" t="n">
         <v>0.2525</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.597</v>
+        <v>2.5916</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1663</v>
+        <v>2.1725</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4307</v>
+        <v>0.4191</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2662</v>
+        <v>3.5086</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8079</v>
+        <v>0.3567</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0741</v>
+        <v>3.1519</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1594</v>
+        <v>2.5615</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2303</v>
+        <v>0.4537</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.0709</v>
+        <v>2.1078</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4256</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4223</v>
+        <v>-0.097</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0033</v>
+        <v>1.0441</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4715</v>
+        <v>0.2996</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3986</v>
+        <v>-0.1571</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.4567</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5421</v>
+        <v>2.5204</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5828</v>
+        <v>1.0553</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0406</v>
+        <v>1.4652</v>
       </c>
       <c r="G21" t="n">
-        <v>3.5086</v>
+        <v>2.0136</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3567</v>
+        <v>-0.352</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1519</v>
+        <v>2.3656</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5615</v>
+        <v>2.5214</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4537</v>
+        <v>0.3634</v>
       </c>
       <c r="L21" t="n">
-        <v>2.1078</v>
+        <v>2.1581</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9471000000000001</v>
+        <v>-0.5078</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.097</v>
+        <v>-0.7153</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0441</v>
+        <v>0.2075</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7499</v>
+        <v>1.5068</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7468</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0031</v>
+        <v>0.6535</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4481</v>
+        <v>1.9096</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4655</v>
+        <v>1.3323</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9826</v>
+        <v>0.5773</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0136</v>
+        <v>2.0824</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.352</v>
+        <v>-0.1259</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3656</v>
+        <v>2.2083</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5214</v>
+        <v>2.2757</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3634</v>
+        <v>0.1176</v>
       </c>
       <c r="L22" t="n">
         <v>2.1581</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5078</v>
+        <v>-0.1933</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7153</v>
+        <v>-0.2435</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2075</v>
+        <v>0.0502</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4345</v>
+        <v>-0.3352</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2636</v>
+        <v>0.2164</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1709</v>
+        <v>-0.5515</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9273</v>
+        <v>1.0008</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7425</v>
+        <v>-0.0133</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1848</v>
+        <v>1.0141</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0824</v>
+        <v>-0.2662</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1259</v>
+        <v>0.8079</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2083</v>
+        <v>-1.0741</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2757</v>
+        <v>0.1594</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1176</v>
+        <v>1.2303</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1581</v>
+        <v>-1.0709</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1933</v>
+        <v>-0.4256</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2435</v>
+        <v>-0.4223</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0502</v>
+        <v>-0.0033</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3175</v>
+        <v>1.8754</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3734</v>
+        <v>1.219</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9441000000000001</v>
+        <v>0.6563</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.8887</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1624</v>
+        <v>0.6342</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2281</v>
+        <v>0.2545</v>
       </c>
       <c r="G24" t="n">
         <v>0.214</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5838</v>
+        <v>0.3705</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.224</v>
+        <v>0.2478</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3598</v>
+        <v>0.1228</v>
       </c>
       <c r="V24" t="n">
         <v>0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4018</v>
+        <v>0.4454</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7517</v>
+        <v>1.1056</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1535</v>
+        <v>-0.6601</v>
       </c>
       <c r="G25" t="n">
         <v>1.4592</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6291</v>
+        <v>0.2181</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3734</v>
+        <v>-0.0196</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2557</v>
+        <v>0.2377</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5361</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6269</v>
+        <v>-0.5419</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8834</v>
+        <v>-0.5295</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2565</v>
+        <v>-0.0123</v>
       </c>
       <c r="G26" t="n">
         <v>-0.1966</v>
@@ -2482,13 +2482,13 @@
         <v>0.6959</v>
       </c>
       <c r="S26" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.1729</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6853</v>
+        <v>0.4165</v>
       </c>
       <c r="V26" t="n">
         <v>-1.214</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>31.194</v>
+        <v>34.3392</v>
       </c>
       <c r="E27" t="n">
-        <v>23.3867</v>
+        <v>23.3868</v>
       </c>
       <c r="F27" t="n">
-        <v>7.8072</v>
+        <v>10.9526</v>
       </c>
       <c r="G27" t="n">
         <v>25.3217</v>
@@ -2533,7 +2533,7 @@
         <v>19.44</v>
       </c>
       <c r="J27" t="n">
-        <v>25.1274</v>
+        <v>25.12740000000001</v>
       </c>
       <c r="K27" t="n">
         <v>10.1052</v>
@@ -2542,7 +2542,7 @@
         <v>15.0222</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1944000000000001</v>
+        <v>0.1944</v>
       </c>
       <c r="N27" t="n">
         <v>-4.2233</v>
@@ -2560,16 +2560,16 @@
         <v>13.9173</v>
       </c>
       <c r="S27" t="n">
-        <v>5.6406</v>
+        <v>8.786</v>
       </c>
       <c r="T27" t="n">
-        <v>4.661099999999999</v>
+        <v>4.6608</v>
       </c>
       <c r="U27" t="n">
-        <v>0.9794999999999998</v>
+        <v>4.125299999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-3.247700000000001</v>
+        <v>-3.2477</v>
       </c>
       <c r="W27" t="n">
         <v>4.0363</v>
